--- a/feedback_surveys/037_essential_oils_massage_feedback--feedback_surveys.xlsx
+++ b/feedback_surveys/037_essential_oils_massage_feedback--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'1_-_not_satisfied',_'value':_'not_satisfied'}</t>
+          <t>1_-_not_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': '1 - Not Satisfied', 'value': 'Not Satisfied'}</t>
+          <t>1 - Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'2_-_somewhat_satisfied',_'value':_'somewhat_satisfied'}</t>
+          <t>2_-_somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': '2 - Somewhat Satisfied', 'value': 'Somewhat Satisfied'}</t>
+          <t>2 - Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'3_-_neutral',_'value':_'neutral'}</t>
+          <t>3_-_neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '3 - Neutral', 'value': 'Neutral'}</t>
+          <t>3 - Neutral</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'4_-_somewhat_satisfied',_'value':_'somewhat_satisfied'}</t>
+          <t>4_-_somewhat_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '4 - Somewhat Satisfied', 'value': 'Somewhat Satisfied'}</t>
+          <t>4 - Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'5_-_very_satisfied',_'value':_'very_satisfied'}</t>
+          <t>5_-_very_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': '5 - Very Satisfied', 'value': 'Very Satisfied'}</t>
+          <t>5 - Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'too_hard',_'value':_'too_hard'}</t>
+          <t>too_hard</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Too Hard', 'value': 'Too Hard'}</t>
+          <t>Too Hard</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'too_soft',_'value':_'too_soft'}</t>
+          <t>too_soft</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Too Soft', 'value': 'Too Soft'}</t>
+          <t>Too Soft</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'just_right',_'value':_'just_right'}</t>
+          <t>just_right</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Just right', 'value': 'Just right'}</t>
+          <t>Just right</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'lavender',_'value':_'lavender'}</t>
+          <t>lavender</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Lavender', 'value': 'Lavender'}</t>
+          <t>Lavender</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'eucalyptus',_'value':_'eucalyptus'}</t>
+          <t>eucalyptus</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Eucalyptus', 'value': 'Eucalyptus'}</t>
+          <t>Eucalyptus</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'frankincense',_'value':_'frankincense'}</t>
+          <t>frankincense</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Frankincense', 'value': 'Frankincense'}</t>
+          <t>Frankincense</t>
         </is>
       </c>
     </row>
